--- a/TOR330 Data/5. Clean Data for Data Visualisation/TOR330_time_travel_issues_df.xlsx
+++ b/TOR330 Data/5. Clean Data for Data Visualisation/TOR330_time_travel_issues_df.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="108">
   <si>
     <t>PK</t>
   </si>
@@ -181,37 +181,31 @@
     <t>TOR330_2024_1367</t>
   </si>
   <si>
-    <t>2024</t>
+    <t>2023</t>
   </si>
   <si>
     <t>TOR330</t>
   </si>
   <si>
-    <t>404</t>
-  </si>
-  <si>
-    <t>1384</t>
-  </si>
-  <si>
-    <t>593</t>
-  </si>
-  <si>
-    <t>405</t>
-  </si>
-  <si>
-    <t>223</t>
-  </si>
-  <si>
-    <t>567</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>431</t>
-  </si>
-  <si>
-    <t>1367</t>
+    <t>334</t>
+  </si>
+  <si>
+    <t>343</t>
+  </si>
+  <si>
+    <t>1391</t>
+  </si>
+  <si>
+    <t>1291</t>
+  </si>
+  <si>
+    <t>423</t>
+  </si>
+  <si>
+    <t>1334</t>
+  </si>
+  <si>
+    <t>1170</t>
   </si>
   <si>
     <t>Finished at Courmayeur</t>
@@ -706,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W34"/>
+  <dimension ref="A1:W62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
@@ -797,19 +791,19 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J2" s="2">
         <v>44456.35815972222</v>
       </c>
       <c r="K2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L2">
         <v>-0.4352546296296296</v>
@@ -827,13 +821,13 @@
         <v>44457.66666666666</v>
       </c>
       <c r="Q2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="R2">
         <v>0.875</v>
       </c>
       <c r="S2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -859,19 +853,19 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J3" s="2">
         <v>44456.22016203704</v>
       </c>
       <c r="K3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L3">
         <v>-0.001018518518518518</v>
@@ -889,13 +883,13 @@
         <v>44456.79166666666</v>
       </c>
       <c r="Q3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R3">
         <v>0.08333333333333333</v>
       </c>
       <c r="S3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -921,22 +915,22 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J4" s="2">
         <v>44452.69923611111</v>
       </c>
       <c r="K4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L4">
         <v>-1.500034722222222</v>
@@ -951,7 +945,7 @@
         <v>110814</v>
       </c>
       <c r="S4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -977,19 +971,19 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J5" s="2">
         <v>44817.16307870371</v>
       </c>
       <c r="K5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L5">
         <v>-0.2740277777777778</v>
@@ -1007,13 +1001,13 @@
         <v>44819.54166666666</v>
       </c>
       <c r="Q5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="R5">
         <v>0.5</v>
       </c>
       <c r="S5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -1039,19 +1033,19 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J6" s="2">
         <v>44817.39240740741</v>
       </c>
       <c r="K6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L6">
         <v>-0.003252314814814815</v>
@@ -1069,13 +1063,13 @@
         <v>44819.04166666666</v>
       </c>
       <c r="Q6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="R6">
         <v>0.08333333333333333</v>
       </c>
       <c r="S6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -1101,19 +1095,19 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J7" s="2">
         <v>44818.26855324074</v>
       </c>
       <c r="K7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L7">
         <v>-0.0005439814814814814</v>
@@ -1131,13 +1125,13 @@
         <v>44819.875</v>
       </c>
       <c r="Q7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="R7">
         <v>0.08333333333333333</v>
       </c>
       <c r="S7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -1163,19 +1157,19 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s">
         <v>76</v>
-      </c>
-      <c r="I8" t="s">
-        <v>78</v>
       </c>
       <c r="J8" s="2">
         <v>44820.53862268518</v>
       </c>
       <c r="K8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L8">
         <v>-0.1621990740740741</v>
@@ -1193,13 +1187,13 @@
         <v>44821.66666666666</v>
       </c>
       <c r="Q8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="R8">
         <v>0.875</v>
       </c>
       <c r="S8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -1225,19 +1219,19 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J9" s="2">
         <v>44819.6137037037</v>
       </c>
       <c r="K9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L9">
         <v>-0.1996296296296296</v>
@@ -1252,7 +1246,7 @@
         <v>362624</v>
       </c>
       <c r="S9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -1278,19 +1272,19 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J10" s="2">
         <v>44820.2553125</v>
       </c>
       <c r="K10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L10">
         <v>-0.0003587962962962963</v>
@@ -1308,13 +1302,13 @@
         <v>44820.79166666666</v>
       </c>
       <c r="Q10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R10">
         <v>0.08333333333333333</v>
       </c>
       <c r="S10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -1340,16 +1334,16 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J11" s="2">
         <v>44816.47495370371</v>
@@ -1367,7 +1361,7 @@
         <v>91436</v>
       </c>
       <c r="S11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T11" t="b">
         <v>0</v>
@@ -1393,16 +1387,16 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J12" s="2">
         <v>44816.80444444445</v>
@@ -1420,7 +1414,7 @@
         <v>119904</v>
       </c>
       <c r="S12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T12" t="b">
         <v>0</v>
@@ -1446,16 +1440,16 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J13" s="2">
         <v>44816.7556712963</v>
@@ -1473,7 +1467,7 @@
         <v>115690</v>
       </c>
       <c r="S13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T13" t="b">
         <v>0</v>
@@ -1499,13 +1493,13 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J14" s="2">
         <v>44818.45127314814</v>
@@ -1523,7 +1517,7 @@
         <v>262190</v>
       </c>
       <c r="S14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T14" t="b">
         <v>0</v>
@@ -1549,13 +1543,13 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J15" s="2">
         <v>44819.50680555555</v>
@@ -1576,13 +1570,13 @@
         <v>44819.95833333334</v>
       </c>
       <c r="Q15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="R15">
         <v>0.08333333333333333</v>
       </c>
       <c r="S15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T15" t="b">
         <v>0</v>
@@ -1608,13 +1602,13 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J16" s="2">
         <v>44818.92413194444</v>
@@ -1635,13 +1629,13 @@
         <v>44819.125</v>
       </c>
       <c r="Q16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="R16">
         <v>0.08333333333333333</v>
       </c>
       <c r="S16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T16" t="b">
         <v>0</v>
@@ -1667,13 +1661,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J17" s="2">
         <v>44818.92489583333</v>
@@ -1694,13 +1688,13 @@
         <v>44819.125</v>
       </c>
       <c r="Q17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="R17">
         <v>0.08333333333333333</v>
       </c>
       <c r="S17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T17" t="b">
         <v>0</v>
@@ -1726,19 +1720,19 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H18" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I18" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J18" s="2">
         <v>45180.90565972222</v>
       </c>
       <c r="K18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L18">
         <v>-0.4725810185185185</v>
@@ -1756,13 +1750,13 @@
         <v>45182</v>
       </c>
       <c r="Q18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R18">
         <v>0.75</v>
       </c>
       <c r="S18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T18" t="b">
         <v>0</v>
@@ -1788,19 +1782,19 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J19" s="2">
         <v>45182.46465277778</v>
       </c>
       <c r="K19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L19">
         <v>-0.0003935185185185185</v>
@@ -1818,13 +1812,13 @@
         <v>45183.04166666666</v>
       </c>
       <c r="Q19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="R19">
         <v>0.08333333333333333</v>
       </c>
       <c r="S19" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T19" t="b">
         <v>0</v>
@@ -1850,19 +1844,19 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J20" s="2">
         <v>45184.5540625</v>
       </c>
       <c r="K20" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L20">
         <v>-0.523912037037037</v>
@@ -1877,7 +1871,7 @@
         <v>436671</v>
       </c>
       <c r="S20" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T20" t="b">
         <v>0</v>
@@ -1903,19 +1897,19 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J21" s="2">
         <v>45180.95467592592</v>
       </c>
       <c r="K21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L21">
         <v>-0.0001157407407407407</v>
@@ -1933,13 +1927,13 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="R21">
         <v>0.08333333333333333</v>
       </c>
       <c r="S21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T21" t="b">
         <v>0</v>
@@ -1965,19 +1959,19 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H22" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I22" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J22" s="2">
         <v>45183.8446412037</v>
       </c>
       <c r="K22" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L22">
         <v>-0.02489583333333333</v>
@@ -1995,13 +1989,13 @@
         <v>45184.79166666666</v>
       </c>
       <c r="Q22" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R22">
         <v>0.08333333333333333</v>
       </c>
       <c r="S22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T22" t="b">
         <v>0</v>
@@ -2027,19 +2021,19 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H23" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I23" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J23" s="2">
         <v>45180.98311342593</v>
       </c>
       <c r="K23" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L23">
         <v>-0.0002083333333333333</v>
@@ -2057,13 +2051,13 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="R23">
         <v>0.08333333333333333</v>
       </c>
       <c r="S23" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T23" t="b">
         <v>0</v>
@@ -2089,19 +2083,19 @@
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I24" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J24" s="2">
         <v>45181.15703703704</v>
       </c>
       <c r="K24" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L24">
         <v>-0.001759259259259259</v>
@@ -2116,7 +2110,7 @@
         <v>143168</v>
       </c>
       <c r="S24" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T24" t="b">
         <v>0</v>
@@ -2129,40 +2123,40 @@
       <c r="A25" t="s">
         <v>46</v>
       </c>
-      <c r="B25" t="s">
-        <v>55</v>
+      <c r="B25">
+        <v>2024</v>
       </c>
       <c r="C25" t="s">
         <v>56</v>
       </c>
-      <c r="D25" t="s">
-        <v>57</v>
+      <c r="D25">
+        <v>404</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J25" s="2">
         <v>45546.77756944444</v>
       </c>
       <c r="K25" t="s">
-        <v>100</v>
-      </c>
-      <c r="L25" s="3">
+        <v>98</v>
+      </c>
+      <c r="L25">
         <v>-0.007534722222222222</v>
       </c>
       <c r="M25">
         <v>-651</v>
       </c>
-      <c r="N25" s="3">
+      <c r="N25">
         <v>3.360902777777778</v>
       </c>
       <c r="O25">
@@ -2172,13 +2166,13 @@
         <v>45547.875</v>
       </c>
       <c r="Q25" t="s">
-        <v>106</v>
-      </c>
-      <c r="R25" s="3">
+        <v>104</v>
+      </c>
+      <c r="R25">
         <v>0.08333333333333333</v>
       </c>
       <c r="S25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T25" t="b">
         <v>0</v>
@@ -2191,47 +2185,47 @@
       <c r="A26" t="s">
         <v>47</v>
       </c>
-      <c r="B26" t="s">
-        <v>55</v>
+      <c r="B26">
+        <v>2024</v>
       </c>
       <c r="C26" t="s">
         <v>56</v>
       </c>
-      <c r="D26" t="s">
-        <v>58</v>
+      <c r="D26">
+        <v>1384</v>
       </c>
       <c r="E26" t="b">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H26" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I26" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J26" s="2">
         <v>45549.00076388889</v>
       </c>
       <c r="K26" t="s">
-        <v>96</v>
-      </c>
-      <c r="L26" s="3">
+        <v>94</v>
+      </c>
+      <c r="L26">
         <v>-0.001527777777777778</v>
       </c>
       <c r="M26">
         <v>-132</v>
       </c>
-      <c r="N26" s="3">
+      <c r="N26">
         <v>5.500763888888889</v>
       </c>
       <c r="O26">
         <v>475266.0000000001</v>
       </c>
       <c r="S26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T26" t="b">
         <v>0</v>
@@ -2244,47 +2238,47 @@
       <c r="A27" t="s">
         <v>48</v>
       </c>
-      <c r="B27" t="s">
-        <v>55</v>
+      <c r="B27">
+        <v>2024</v>
       </c>
       <c r="C27" t="s">
         <v>56</v>
       </c>
-      <c r="D27" t="s">
-        <v>59</v>
+      <c r="D27">
+        <v>593</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H27" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I27" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J27" s="2">
         <v>45548.98298611111</v>
       </c>
       <c r="K27" t="s">
-        <v>96</v>
-      </c>
-      <c r="L27" s="3">
+        <v>94</v>
+      </c>
+      <c r="L27">
         <v>-0.01901620370370371</v>
       </c>
       <c r="M27">
         <v>-1643</v>
       </c>
-      <c r="N27" s="3">
+      <c r="N27">
         <v>5.566319444444445</v>
       </c>
       <c r="O27">
         <v>480930.0000000001</v>
       </c>
       <c r="S27" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T27" t="b">
         <v>0</v>
@@ -2297,47 +2291,47 @@
       <c r="A28" t="s">
         <v>49</v>
       </c>
-      <c r="B28" t="s">
-        <v>55</v>
+      <c r="B28">
+        <v>2024</v>
       </c>
       <c r="C28" t="s">
         <v>56</v>
       </c>
-      <c r="D28" t="s">
-        <v>60</v>
+      <c r="D28">
+        <v>405</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H28" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I28" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J28" s="2">
         <v>45549.00091435185</v>
       </c>
       <c r="K28" t="s">
-        <v>96</v>
-      </c>
-      <c r="L28" s="3">
+        <v>94</v>
+      </c>
+      <c r="L28">
         <v>-0.001319444444444444</v>
       </c>
       <c r="M28">
         <v>-114</v>
       </c>
-      <c r="N28" s="3">
+      <c r="N28">
         <v>5.584247685185185</v>
       </c>
       <c r="O28">
         <v>482479.0000000001</v>
       </c>
       <c r="S28" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T28" t="b">
         <v>0</v>
@@ -2350,47 +2344,47 @@
       <c r="A29" t="s">
         <v>50</v>
       </c>
-      <c r="B29" t="s">
-        <v>55</v>
+      <c r="B29">
+        <v>2024</v>
       </c>
       <c r="C29" t="s">
         <v>56</v>
       </c>
-      <c r="D29" t="s">
-        <v>61</v>
+      <c r="D29">
+        <v>223</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I29" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J29" s="2">
         <v>45549.00192129629</v>
       </c>
       <c r="K29" t="s">
-        <v>96</v>
-      </c>
-      <c r="L29" s="3">
+        <v>94</v>
+      </c>
+      <c r="L29">
         <v>-0.0002430555555555555</v>
       </c>
       <c r="M29">
         <v>-21</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29">
         <v>5.585254629629629</v>
       </c>
       <c r="O29">
         <v>482566.0000000001</v>
       </c>
       <c r="S29" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T29" t="b">
         <v>0</v>
@@ -2403,47 +2397,47 @@
       <c r="A30" t="s">
         <v>51</v>
       </c>
-      <c r="B30" t="s">
-        <v>55</v>
+      <c r="B30">
+        <v>2024</v>
       </c>
       <c r="C30" t="s">
         <v>56</v>
       </c>
-      <c r="D30" t="s">
-        <v>62</v>
+      <c r="D30">
+        <v>567</v>
       </c>
       <c r="E30" t="b">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H30" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I30" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J30" s="2">
         <v>45548.99665509259</v>
       </c>
       <c r="K30" t="s">
-        <v>96</v>
-      </c>
-      <c r="L30" s="3">
+        <v>94</v>
+      </c>
+      <c r="L30">
         <v>-0.005416666666666667</v>
       </c>
       <c r="M30">
         <v>-468.0000000000001</v>
       </c>
-      <c r="N30" s="3">
+      <c r="N30">
         <v>5.579988425925926</v>
       </c>
       <c r="O30">
         <v>482111.0000000001</v>
       </c>
       <c r="S30" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T30" t="b">
         <v>0</v>
@@ -2456,47 +2450,47 @@
       <c r="A31" t="s">
         <v>52</v>
       </c>
-      <c r="B31" t="s">
-        <v>55</v>
+      <c r="B31">
+        <v>2024</v>
       </c>
       <c r="C31" t="s">
         <v>56</v>
       </c>
-      <c r="D31" t="s">
-        <v>63</v>
+      <c r="D31">
+        <v>38</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H31" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I31" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J31" s="2">
         <v>45547.86248842593</v>
       </c>
       <c r="K31" t="s">
-        <v>101</v>
-      </c>
-      <c r="L31" s="3">
+        <v>99</v>
+      </c>
+      <c r="L31">
         <v>-0.7659490740740741</v>
       </c>
       <c r="M31">
         <v>-66178</v>
       </c>
-      <c r="N31" s="3">
+      <c r="N31">
         <v>4.445821759259259</v>
       </c>
       <c r="O31">
         <v>384119</v>
       </c>
       <c r="S31" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T31" t="b">
         <v>0</v>
@@ -2509,47 +2503,47 @@
       <c r="A32" t="s">
         <v>53</v>
       </c>
-      <c r="B32" t="s">
-        <v>55</v>
+      <c r="B32">
+        <v>2024</v>
       </c>
       <c r="C32" t="s">
         <v>56</v>
       </c>
-      <c r="D32" t="s">
-        <v>64</v>
+      <c r="D32">
+        <v>431</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H32" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I32" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J32" s="2">
         <v>45547.67736111111</v>
       </c>
       <c r="K32" t="s">
-        <v>101</v>
-      </c>
-      <c r="L32" s="3">
+        <v>99</v>
+      </c>
+      <c r="L32">
         <v>-0.6936458333333333</v>
       </c>
       <c r="M32">
         <v>-59931.00000000001</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32">
         <v>4.260694444444445</v>
       </c>
       <c r="O32">
         <v>368124</v>
       </c>
       <c r="S32" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T32" t="b">
         <v>0</v>
@@ -2562,47 +2556,47 @@
       <c r="A33" t="s">
         <v>53</v>
       </c>
-      <c r="B33" t="s">
-        <v>55</v>
+      <c r="B33">
+        <v>2024</v>
       </c>
       <c r="C33" t="s">
         <v>56</v>
       </c>
-      <c r="D33" t="s">
-        <v>64</v>
+      <c r="D33">
+        <v>431</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H33" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I33" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J33" s="2">
         <v>45547.88945601852</v>
       </c>
       <c r="K33" t="s">
-        <v>101</v>
-      </c>
-      <c r="L33" s="3">
+        <v>99</v>
+      </c>
+      <c r="L33">
         <v>-0.8231597222222222</v>
       </c>
       <c r="M33">
         <v>-71121</v>
       </c>
-      <c r="N33" s="3">
+      <c r="N33">
         <v>4.472789351851852</v>
       </c>
       <c r="O33">
         <v>386449</v>
       </c>
       <c r="S33" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T33" t="b">
         <v>0</v>
@@ -2615,43 +2609,43 @@
       <c r="A34" t="s">
         <v>54</v>
       </c>
-      <c r="B34" t="s">
-        <v>55</v>
+      <c r="B34">
+        <v>2024</v>
       </c>
       <c r="C34" t="s">
         <v>56</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34">
+        <v>1367</v>
+      </c>
+      <c r="E34" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" t="s">
         <v>65</v>
       </c>
-      <c r="E34" t="b">
-        <v>0</v>
-      </c>
-      <c r="F34" t="s">
-        <v>67</v>
-      </c>
       <c r="G34" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H34" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I34" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J34" s="2">
         <v>45545.14299768519</v>
       </c>
       <c r="K34" t="s">
-        <v>67</v>
-      </c>
-      <c r="L34" s="3">
+        <v>65</v>
+      </c>
+      <c r="L34">
         <v>-0.0003587962962962963</v>
       </c>
       <c r="M34">
         <v>-31</v>
       </c>
-      <c r="N34" s="3">
+      <c r="N34">
         <v>1.642997685185185</v>
       </c>
       <c r="O34">
@@ -2661,18 +2655,1682 @@
         <v>45545.33333333334</v>
       </c>
       <c r="Q34" t="s">
-        <v>108</v>
-      </c>
-      <c r="R34" s="3">
+        <v>106</v>
+      </c>
+      <c r="R34">
         <v>0.08333333333333333</v>
       </c>
       <c r="S34" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T34" t="b">
         <v>0</v>
       </c>
       <c r="U34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35">
+        <v>2023</v>
+      </c>
+      <c r="C35" t="s">
+        <v>56</v>
+      </c>
+      <c r="D35">
+        <v>334</v>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
+        <v>64</v>
+      </c>
+      <c r="H35" t="s">
+        <v>74</v>
+      </c>
+      <c r="I35" t="s">
+        <v>86</v>
+      </c>
+      <c r="J35" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K35" t="s">
+        <v>98</v>
+      </c>
+      <c r="L35">
+        <v>-0.4725810185185185</v>
+      </c>
+      <c r="M35">
+        <v>-40831</v>
+      </c>
+      <c r="N35">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O35">
+        <v>128649</v>
+      </c>
+      <c r="P35" s="2">
+        <v>45182</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>105</v>
+      </c>
+      <c r="R35">
+        <v>0.75</v>
+      </c>
+      <c r="S35" t="s">
+        <v>107</v>
+      </c>
+      <c r="T35" t="b">
+        <v>0</v>
+      </c>
+      <c r="U35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36">
+        <v>2023</v>
+      </c>
+      <c r="C36" t="s">
+        <v>56</v>
+      </c>
+      <c r="D36">
+        <v>343</v>
+      </c>
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>64</v>
+      </c>
+      <c r="H36" t="s">
+        <v>74</v>
+      </c>
+      <c r="I36" t="s">
+        <v>80</v>
+      </c>
+      <c r="J36" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K36" t="s">
+        <v>94</v>
+      </c>
+      <c r="L36">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M36">
+        <v>-34</v>
+      </c>
+      <c r="N36">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O36">
+        <v>263346</v>
+      </c>
+      <c r="P36" s="2">
+        <v>45183.04166666666</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>103</v>
+      </c>
+      <c r="R36">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="S36" t="s">
+        <v>107</v>
+      </c>
+      <c r="T36" t="b">
+        <v>0</v>
+      </c>
+      <c r="U36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
+      <c r="A37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37">
+        <v>2023</v>
+      </c>
+      <c r="C37" t="s">
+        <v>56</v>
+      </c>
+      <c r="D37">
+        <v>1391</v>
+      </c>
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="s">
+        <v>64</v>
+      </c>
+      <c r="H37" t="s">
+        <v>75</v>
+      </c>
+      <c r="I37" t="s">
+        <v>87</v>
+      </c>
+      <c r="J37" s="2">
+        <v>45184.5540625</v>
+      </c>
+      <c r="K37" t="s">
+        <v>99</v>
+      </c>
+      <c r="L37">
+        <v>-0.523912037037037</v>
+      </c>
+      <c r="M37">
+        <v>-45266</v>
+      </c>
+      <c r="N37">
+        <v>5.0540625</v>
+      </c>
+      <c r="O37">
+        <v>436671</v>
+      </c>
+      <c r="S37" t="s">
+        <v>107</v>
+      </c>
+      <c r="T37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21">
+      <c r="A38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38">
+        <v>2023</v>
+      </c>
+      <c r="C38" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38">
+        <v>1291</v>
+      </c>
+      <c r="E38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>64</v>
+      </c>
+      <c r="H38" t="s">
+        <v>75</v>
+      </c>
+      <c r="I38" t="s">
+        <v>88</v>
+      </c>
+      <c r="J38" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K38" t="s">
+        <v>99</v>
+      </c>
+      <c r="L38">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M38">
+        <v>-10</v>
+      </c>
+      <c r="N38">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O38">
+        <v>125684</v>
+      </c>
+      <c r="P38" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>106</v>
+      </c>
+      <c r="R38">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="S38" t="s">
+        <v>107</v>
+      </c>
+      <c r="T38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
+      <c r="A39" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39">
+        <v>2023</v>
+      </c>
+      <c r="C39" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39">
+        <v>423</v>
+      </c>
+      <c r="E39" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" t="s">
+        <v>64</v>
+      </c>
+      <c r="H39" t="s">
+        <v>74</v>
+      </c>
+      <c r="I39" t="s">
+        <v>77</v>
+      </c>
+      <c r="J39" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K39" t="s">
+        <v>99</v>
+      </c>
+      <c r="L39">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M39">
+        <v>-2151</v>
+      </c>
+      <c r="N39">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O39">
+        <v>382577</v>
+      </c>
+      <c r="P39" s="2">
+        <v>45184.79166666666</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>101</v>
+      </c>
+      <c r="R39">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="S39" t="s">
+        <v>107</v>
+      </c>
+      <c r="T39" t="b">
+        <v>0</v>
+      </c>
+      <c r="U39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
+      <c r="A40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40">
+        <v>2023</v>
+      </c>
+      <c r="C40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40">
+        <v>1334</v>
+      </c>
+      <c r="E40" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>64</v>
+      </c>
+      <c r="H40" t="s">
+        <v>75</v>
+      </c>
+      <c r="I40" t="s">
+        <v>88</v>
+      </c>
+      <c r="J40" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K40" t="s">
+        <v>99</v>
+      </c>
+      <c r="L40">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M40">
+        <v>-18</v>
+      </c>
+      <c r="N40">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O40">
+        <v>128141</v>
+      </c>
+      <c r="P40" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>106</v>
+      </c>
+      <c r="R40">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="S40" t="s">
+        <v>107</v>
+      </c>
+      <c r="T40" t="b">
+        <v>0</v>
+      </c>
+      <c r="U40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
+      <c r="A41" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41">
+        <v>2023</v>
+      </c>
+      <c r="C41" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41">
+        <v>1170</v>
+      </c>
+      <c r="E41" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" t="s">
+        <v>64</v>
+      </c>
+      <c r="H41" t="s">
+        <v>75</v>
+      </c>
+      <c r="I41" t="s">
+        <v>89</v>
+      </c>
+      <c r="J41" s="2">
+        <v>45181.15703703704</v>
+      </c>
+      <c r="K41" t="s">
+        <v>99</v>
+      </c>
+      <c r="L41">
+        <v>-0.001759259259259259</v>
+      </c>
+      <c r="M41">
+        <v>-152</v>
+      </c>
+      <c r="N41">
+        <v>1.657037037037037</v>
+      </c>
+      <c r="O41">
+        <v>143168</v>
+      </c>
+      <c r="S41" t="s">
+        <v>107</v>
+      </c>
+      <c r="T41" t="b">
+        <v>0</v>
+      </c>
+      <c r="U41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
+      <c r="A42" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42">
+        <v>2023</v>
+      </c>
+      <c r="C42" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42">
+        <v>334</v>
+      </c>
+      <c r="E42" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" t="s">
+        <v>64</v>
+      </c>
+      <c r="H42" t="s">
+        <v>74</v>
+      </c>
+      <c r="I42" t="s">
+        <v>86</v>
+      </c>
+      <c r="J42" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K42" t="s">
+        <v>98</v>
+      </c>
+      <c r="L42">
+        <v>-0.4725810185185185</v>
+      </c>
+      <c r="M42">
+        <v>-40831</v>
+      </c>
+      <c r="N42">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O42">
+        <v>128649</v>
+      </c>
+      <c r="P42" s="2">
+        <v>45182</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>105</v>
+      </c>
+      <c r="R42">
+        <v>0.75</v>
+      </c>
+      <c r="S42" t="s">
+        <v>107</v>
+      </c>
+      <c r="T42" t="b">
+        <v>0</v>
+      </c>
+      <c r="U42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
+      <c r="A43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43">
+        <v>2023</v>
+      </c>
+      <c r="C43" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43">
+        <v>343</v>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" t="s">
+        <v>64</v>
+      </c>
+      <c r="H43" t="s">
+        <v>74</v>
+      </c>
+      <c r="I43" t="s">
+        <v>80</v>
+      </c>
+      <c r="J43" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K43" t="s">
+        <v>94</v>
+      </c>
+      <c r="L43">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M43">
+        <v>-34</v>
+      </c>
+      <c r="N43">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O43">
+        <v>263346</v>
+      </c>
+      <c r="P43" s="2">
+        <v>45183.04166666666</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>103</v>
+      </c>
+      <c r="R43">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="S43" t="s">
+        <v>107</v>
+      </c>
+      <c r="T43" t="b">
+        <v>0</v>
+      </c>
+      <c r="U43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21">
+      <c r="A44" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44">
+        <v>2023</v>
+      </c>
+      <c r="C44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44">
+        <v>1391</v>
+      </c>
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" t="s">
+        <v>64</v>
+      </c>
+      <c r="H44" t="s">
+        <v>75</v>
+      </c>
+      <c r="I44" t="s">
+        <v>87</v>
+      </c>
+      <c r="J44" s="2">
+        <v>45184.5540625</v>
+      </c>
+      <c r="K44" t="s">
+        <v>99</v>
+      </c>
+      <c r="L44">
+        <v>-0.523912037037037</v>
+      </c>
+      <c r="M44">
+        <v>-45266</v>
+      </c>
+      <c r="N44">
+        <v>5.0540625</v>
+      </c>
+      <c r="O44">
+        <v>436671</v>
+      </c>
+      <c r="S44" t="s">
+        <v>107</v>
+      </c>
+      <c r="T44" t="b">
+        <v>0</v>
+      </c>
+      <c r="U44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21">
+      <c r="A45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45">
+        <v>2023</v>
+      </c>
+      <c r="C45" t="s">
+        <v>56</v>
+      </c>
+      <c r="D45">
+        <v>1291</v>
+      </c>
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" t="s">
+        <v>64</v>
+      </c>
+      <c r="H45" t="s">
+        <v>75</v>
+      </c>
+      <c r="I45" t="s">
+        <v>88</v>
+      </c>
+      <c r="J45" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K45" t="s">
+        <v>99</v>
+      </c>
+      <c r="L45">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M45">
+        <v>-10</v>
+      </c>
+      <c r="N45">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O45">
+        <v>125684</v>
+      </c>
+      <c r="P45" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>106</v>
+      </c>
+      <c r="R45">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="S45" t="s">
+        <v>107</v>
+      </c>
+      <c r="T45" t="b">
+        <v>0</v>
+      </c>
+      <c r="U45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
+      <c r="A46" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46">
+        <v>2023</v>
+      </c>
+      <c r="C46" t="s">
+        <v>56</v>
+      </c>
+      <c r="D46">
+        <v>423</v>
+      </c>
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" t="s">
+        <v>64</v>
+      </c>
+      <c r="H46" t="s">
+        <v>74</v>
+      </c>
+      <c r="I46" t="s">
+        <v>77</v>
+      </c>
+      <c r="J46" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K46" t="s">
+        <v>99</v>
+      </c>
+      <c r="L46">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M46">
+        <v>-2151</v>
+      </c>
+      <c r="N46">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O46">
+        <v>382577</v>
+      </c>
+      <c r="P46" s="2">
+        <v>45184.79166666666</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>101</v>
+      </c>
+      <c r="R46">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="S46" t="s">
+        <v>107</v>
+      </c>
+      <c r="T46" t="b">
+        <v>0</v>
+      </c>
+      <c r="U46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21">
+      <c r="A47" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47">
+        <v>2023</v>
+      </c>
+      <c r="C47" t="s">
+        <v>56</v>
+      </c>
+      <c r="D47">
+        <v>1334</v>
+      </c>
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" t="s">
+        <v>64</v>
+      </c>
+      <c r="H47" t="s">
+        <v>75</v>
+      </c>
+      <c r="I47" t="s">
+        <v>88</v>
+      </c>
+      <c r="J47" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K47" t="s">
+        <v>99</v>
+      </c>
+      <c r="L47">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M47">
+        <v>-18</v>
+      </c>
+      <c r="N47">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O47">
+        <v>128141</v>
+      </c>
+      <c r="P47" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>106</v>
+      </c>
+      <c r="R47">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="S47" t="s">
+        <v>107</v>
+      </c>
+      <c r="T47" t="b">
+        <v>0</v>
+      </c>
+      <c r="U47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21">
+      <c r="A48" t="s">
+        <v>45</v>
+      </c>
+      <c r="B48">
+        <v>2023</v>
+      </c>
+      <c r="C48" t="s">
+        <v>56</v>
+      </c>
+      <c r="D48">
+        <v>1170</v>
+      </c>
+      <c r="E48" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" t="s">
+        <v>64</v>
+      </c>
+      <c r="H48" t="s">
+        <v>75</v>
+      </c>
+      <c r="I48" t="s">
+        <v>89</v>
+      </c>
+      <c r="J48" s="2">
+        <v>45181.15703703704</v>
+      </c>
+      <c r="K48" t="s">
+        <v>99</v>
+      </c>
+      <c r="L48">
+        <v>-0.001759259259259259</v>
+      </c>
+      <c r="M48">
+        <v>-152</v>
+      </c>
+      <c r="N48">
+        <v>1.657037037037037</v>
+      </c>
+      <c r="O48">
+        <v>143168</v>
+      </c>
+      <c r="S48" t="s">
+        <v>107</v>
+      </c>
+      <c r="T48" t="b">
+        <v>0</v>
+      </c>
+      <c r="U48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21">
+      <c r="A49" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49">
+        <v>2023</v>
+      </c>
+      <c r="C49" t="s">
+        <v>56</v>
+      </c>
+      <c r="D49">
+        <v>334</v>
+      </c>
+      <c r="E49" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" t="s">
+        <v>64</v>
+      </c>
+      <c r="H49" t="s">
+        <v>74</v>
+      </c>
+      <c r="I49" t="s">
+        <v>86</v>
+      </c>
+      <c r="J49" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K49" t="s">
+        <v>98</v>
+      </c>
+      <c r="L49">
+        <v>-0.4725810185185185</v>
+      </c>
+      <c r="M49">
+        <v>-40831</v>
+      </c>
+      <c r="N49">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O49">
+        <v>128649</v>
+      </c>
+      <c r="P49" s="2">
+        <v>45182</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>105</v>
+      </c>
+      <c r="R49">
+        <v>0.75</v>
+      </c>
+      <c r="S49" t="s">
+        <v>107</v>
+      </c>
+      <c r="T49" t="b">
+        <v>0</v>
+      </c>
+      <c r="U49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21">
+      <c r="A50" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50">
+        <v>2023</v>
+      </c>
+      <c r="C50" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50">
+        <v>343</v>
+      </c>
+      <c r="E50" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" t="s">
+        <v>64</v>
+      </c>
+      <c r="H50" t="s">
+        <v>74</v>
+      </c>
+      <c r="I50" t="s">
+        <v>80</v>
+      </c>
+      <c r="J50" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K50" t="s">
+        <v>94</v>
+      </c>
+      <c r="L50">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M50">
+        <v>-34</v>
+      </c>
+      <c r="N50">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O50">
+        <v>263346</v>
+      </c>
+      <c r="P50" s="2">
+        <v>45183.04166666666</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>103</v>
+      </c>
+      <c r="R50">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="S50" t="s">
+        <v>107</v>
+      </c>
+      <c r="T50" t="b">
+        <v>0</v>
+      </c>
+      <c r="U50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21">
+      <c r="A51" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51">
+        <v>2023</v>
+      </c>
+      <c r="C51" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51">
+        <v>1391</v>
+      </c>
+      <c r="E51" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" t="s">
+        <v>64</v>
+      </c>
+      <c r="H51" t="s">
+        <v>75</v>
+      </c>
+      <c r="I51" t="s">
+        <v>87</v>
+      </c>
+      <c r="J51" s="2">
+        <v>45184.5540625</v>
+      </c>
+      <c r="K51" t="s">
+        <v>99</v>
+      </c>
+      <c r="L51">
+        <v>-0.523912037037037</v>
+      </c>
+      <c r="M51">
+        <v>-45266</v>
+      </c>
+      <c r="N51">
+        <v>5.0540625</v>
+      </c>
+      <c r="O51">
+        <v>436671</v>
+      </c>
+      <c r="S51" t="s">
+        <v>107</v>
+      </c>
+      <c r="T51" t="b">
+        <v>0</v>
+      </c>
+      <c r="U51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21">
+      <c r="A52" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52">
+        <v>2023</v>
+      </c>
+      <c r="C52" t="s">
+        <v>56</v>
+      </c>
+      <c r="D52">
+        <v>1291</v>
+      </c>
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" t="s">
+        <v>64</v>
+      </c>
+      <c r="H52" t="s">
+        <v>75</v>
+      </c>
+      <c r="I52" t="s">
+        <v>88</v>
+      </c>
+      <c r="J52" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K52" t="s">
+        <v>99</v>
+      </c>
+      <c r="L52">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M52">
+        <v>-10</v>
+      </c>
+      <c r="N52">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O52">
+        <v>125684</v>
+      </c>
+      <c r="P52" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>106</v>
+      </c>
+      <c r="R52">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="S52" t="s">
+        <v>107</v>
+      </c>
+      <c r="T52" t="b">
+        <v>0</v>
+      </c>
+      <c r="U52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21">
+      <c r="A53" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53">
+        <v>2023</v>
+      </c>
+      <c r="C53" t="s">
+        <v>56</v>
+      </c>
+      <c r="D53">
+        <v>423</v>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" t="s">
+        <v>64</v>
+      </c>
+      <c r="H53" t="s">
+        <v>74</v>
+      </c>
+      <c r="I53" t="s">
+        <v>77</v>
+      </c>
+      <c r="J53" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K53" t="s">
+        <v>99</v>
+      </c>
+      <c r="L53">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M53">
+        <v>-2151</v>
+      </c>
+      <c r="N53">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O53">
+        <v>382577</v>
+      </c>
+      <c r="P53" s="2">
+        <v>45184.79166666666</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>101</v>
+      </c>
+      <c r="R53">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="S53" t="s">
+        <v>107</v>
+      </c>
+      <c r="T53" t="b">
+        <v>0</v>
+      </c>
+      <c r="U53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21">
+      <c r="A54" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54">
+        <v>2023</v>
+      </c>
+      <c r="C54" t="s">
+        <v>56</v>
+      </c>
+      <c r="D54">
+        <v>1334</v>
+      </c>
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54" t="s">
+        <v>64</v>
+      </c>
+      <c r="H54" t="s">
+        <v>75</v>
+      </c>
+      <c r="I54" t="s">
+        <v>88</v>
+      </c>
+      <c r="J54" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K54" t="s">
+        <v>99</v>
+      </c>
+      <c r="L54">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M54">
+        <v>-18</v>
+      </c>
+      <c r="N54">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O54">
+        <v>128141</v>
+      </c>
+      <c r="P54" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>106</v>
+      </c>
+      <c r="R54">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="S54" t="s">
+        <v>107</v>
+      </c>
+      <c r="T54" t="b">
+        <v>0</v>
+      </c>
+      <c r="U54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21">
+      <c r="A55" t="s">
+        <v>45</v>
+      </c>
+      <c r="B55">
+        <v>2023</v>
+      </c>
+      <c r="C55" t="s">
+        <v>56</v>
+      </c>
+      <c r="D55">
+        <v>1170</v>
+      </c>
+      <c r="E55" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55" t="s">
+        <v>64</v>
+      </c>
+      <c r="H55" t="s">
+        <v>75</v>
+      </c>
+      <c r="I55" t="s">
+        <v>89</v>
+      </c>
+      <c r="J55" s="2">
+        <v>45181.15703703704</v>
+      </c>
+      <c r="K55" t="s">
+        <v>99</v>
+      </c>
+      <c r="L55">
+        <v>-0.001759259259259259</v>
+      </c>
+      <c r="M55">
+        <v>-152</v>
+      </c>
+      <c r="N55">
+        <v>1.657037037037037</v>
+      </c>
+      <c r="O55">
+        <v>143168</v>
+      </c>
+      <c r="S55" t="s">
+        <v>107</v>
+      </c>
+      <c r="T55" t="b">
+        <v>0</v>
+      </c>
+      <c r="U55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21">
+      <c r="A56" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" t="s">
+        <v>55</v>
+      </c>
+      <c r="C56" t="s">
+        <v>56</v>
+      </c>
+      <c r="D56" t="s">
+        <v>57</v>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" t="s">
+        <v>64</v>
+      </c>
+      <c r="H56" t="s">
+        <v>74</v>
+      </c>
+      <c r="I56" t="s">
+        <v>86</v>
+      </c>
+      <c r="J56" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K56" t="s">
+        <v>98</v>
+      </c>
+      <c r="L56" s="3">
+        <v>-0.4725810185185185</v>
+      </c>
+      <c r="M56">
+        <v>-40831</v>
+      </c>
+      <c r="N56" s="3">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O56">
+        <v>128649</v>
+      </c>
+      <c r="P56" s="2">
+        <v>45182</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>105</v>
+      </c>
+      <c r="R56" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="S56" t="s">
+        <v>107</v>
+      </c>
+      <c r="T56" t="b">
+        <v>0</v>
+      </c>
+      <c r="U56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21">
+      <c r="A57" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" t="s">
+        <v>55</v>
+      </c>
+      <c r="C57" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57" t="s">
+        <v>58</v>
+      </c>
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" t="s">
+        <v>64</v>
+      </c>
+      <c r="H57" t="s">
+        <v>74</v>
+      </c>
+      <c r="I57" t="s">
+        <v>80</v>
+      </c>
+      <c r="J57" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K57" t="s">
+        <v>94</v>
+      </c>
+      <c r="L57" s="3">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M57">
+        <v>-34</v>
+      </c>
+      <c r="N57" s="3">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O57">
+        <v>263346</v>
+      </c>
+      <c r="P57" s="2">
+        <v>45183.04166666666</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>103</v>
+      </c>
+      <c r="R57" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="S57" t="s">
+        <v>107</v>
+      </c>
+      <c r="T57" t="b">
+        <v>0</v>
+      </c>
+      <c r="U57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21">
+      <c r="A58" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" t="s">
+        <v>55</v>
+      </c>
+      <c r="C58" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" t="s">
+        <v>59</v>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" t="s">
+        <v>64</v>
+      </c>
+      <c r="H58" t="s">
+        <v>75</v>
+      </c>
+      <c r="I58" t="s">
+        <v>87</v>
+      </c>
+      <c r="J58" s="2">
+        <v>45184.5540625</v>
+      </c>
+      <c r="K58" t="s">
+        <v>99</v>
+      </c>
+      <c r="L58" s="3">
+        <v>-0.523912037037037</v>
+      </c>
+      <c r="M58">
+        <v>-45266</v>
+      </c>
+      <c r="N58" s="3">
+        <v>5.0540625</v>
+      </c>
+      <c r="O58">
+        <v>436671</v>
+      </c>
+      <c r="S58" t="s">
+        <v>107</v>
+      </c>
+      <c r="T58" t="b">
+        <v>0</v>
+      </c>
+      <c r="U58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21">
+      <c r="A59" t="s">
+        <v>42</v>
+      </c>
+      <c r="B59" t="s">
+        <v>55</v>
+      </c>
+      <c r="C59" t="s">
+        <v>56</v>
+      </c>
+      <c r="D59" t="s">
+        <v>60</v>
+      </c>
+      <c r="E59" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>64</v>
+      </c>
+      <c r="H59" t="s">
+        <v>75</v>
+      </c>
+      <c r="I59" t="s">
+        <v>88</v>
+      </c>
+      <c r="J59" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K59" t="s">
+        <v>99</v>
+      </c>
+      <c r="L59" s="3">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M59">
+        <v>-10</v>
+      </c>
+      <c r="N59" s="3">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O59">
+        <v>125684</v>
+      </c>
+      <c r="P59" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>106</v>
+      </c>
+      <c r="R59" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="S59" t="s">
+        <v>107</v>
+      </c>
+      <c r="T59" t="b">
+        <v>0</v>
+      </c>
+      <c r="U59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21">
+      <c r="A60" t="s">
+        <v>43</v>
+      </c>
+      <c r="B60" t="s">
+        <v>55</v>
+      </c>
+      <c r="C60" t="s">
+        <v>56</v>
+      </c>
+      <c r="D60" t="s">
+        <v>61</v>
+      </c>
+      <c r="E60" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" t="s">
+        <v>64</v>
+      </c>
+      <c r="H60" t="s">
+        <v>74</v>
+      </c>
+      <c r="I60" t="s">
+        <v>77</v>
+      </c>
+      <c r="J60" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K60" t="s">
+        <v>99</v>
+      </c>
+      <c r="L60" s="3">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M60">
+        <v>-2151</v>
+      </c>
+      <c r="N60" s="3">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O60">
+        <v>382577</v>
+      </c>
+      <c r="P60" s="2">
+        <v>45184.79166666666</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>101</v>
+      </c>
+      <c r="R60" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="S60" t="s">
+        <v>107</v>
+      </c>
+      <c r="T60" t="b">
+        <v>0</v>
+      </c>
+      <c r="U60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21">
+      <c r="A61" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" t="s">
+        <v>55</v>
+      </c>
+      <c r="C61" t="s">
+        <v>56</v>
+      </c>
+      <c r="D61" t="s">
+        <v>62</v>
+      </c>
+      <c r="E61" t="b">
+        <v>1</v>
+      </c>
+      <c r="F61" t="s">
+        <v>64</v>
+      </c>
+      <c r="H61" t="s">
+        <v>75</v>
+      </c>
+      <c r="I61" t="s">
+        <v>88</v>
+      </c>
+      <c r="J61" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K61" t="s">
+        <v>99</v>
+      </c>
+      <c r="L61" s="3">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M61">
+        <v>-18</v>
+      </c>
+      <c r="N61" s="3">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O61">
+        <v>128141</v>
+      </c>
+      <c r="P61" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>106</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="S61" t="s">
+        <v>107</v>
+      </c>
+      <c r="T61" t="b">
+        <v>0</v>
+      </c>
+      <c r="U61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21">
+      <c r="A62" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" t="s">
+        <v>55</v>
+      </c>
+      <c r="C62" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" t="s">
+        <v>63</v>
+      </c>
+      <c r="E62" t="b">
+        <v>1</v>
+      </c>
+      <c r="F62" t="s">
+        <v>64</v>
+      </c>
+      <c r="H62" t="s">
+        <v>75</v>
+      </c>
+      <c r="I62" t="s">
+        <v>89</v>
+      </c>
+      <c r="J62" s="2">
+        <v>45181.15703703704</v>
+      </c>
+      <c r="K62" t="s">
+        <v>99</v>
+      </c>
+      <c r="L62" s="3">
+        <v>-0.001759259259259259</v>
+      </c>
+      <c r="M62">
+        <v>-152</v>
+      </c>
+      <c r="N62" s="3">
+        <v>1.657037037037037</v>
+      </c>
+      <c r="O62">
+        <v>143168</v>
+      </c>
+      <c r="S62" t="s">
+        <v>107</v>
+      </c>
+      <c r="T62" t="b">
+        <v>0</v>
+      </c>
+      <c r="U62" t="b">
         <v>0</v>
       </c>
     </row>
